--- a/dataset_t6_grouped/results2/G4/G4_T8482_W0038F0001T0006Z000C1N21_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T8482_W0038F0001T0006Z000C1N21_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>72.27262184525465</v>
+        <v>11.74430104985388</v>
       </c>
       <c r="D2" t="n">
-        <v>70.00596113487479</v>
+        <v>11.37596868441715</v>
       </c>
       <c r="E2" t="n">
-        <v>19.59054581147163</v>
+        <v>3.183463694364141</v>
       </c>
       <c r="F2" t="n">
-        <v>19.94390974231333</v>
+        <v>3.240885333125916</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>35.80128615234656</v>
+        <v>5.817708999756317</v>
       </c>
       <c r="D3" t="n">
-        <v>33.08752800980686</v>
+        <v>5.376723301593615</v>
       </c>
       <c r="E3" t="n">
-        <v>19.59054581147163</v>
+        <v>3.183463694364141</v>
       </c>
       <c r="F3" t="n">
-        <v>19.94390974231333</v>
+        <v>3.240885333125916</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>39.64524507325682</v>
+        <v>6.442352324404233</v>
       </c>
       <c r="D4" t="n">
-        <v>39.13660717065455</v>
+        <v>6.359698665231365</v>
       </c>
       <c r="E4" t="n">
-        <v>19.59054581147163</v>
+        <v>3.183463694364141</v>
       </c>
       <c r="F4" t="n">
-        <v>19.94390974231333</v>
+        <v>3.240885333125916</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>26.08800514963484</v>
+        <v>4.239300836815661</v>
       </c>
       <c r="D5" t="n">
-        <v>26.02977382788022</v>
+        <v>4.229838247030536</v>
       </c>
       <c r="E5" t="n">
-        <v>19.59054581147163</v>
+        <v>3.183463694364141</v>
       </c>
       <c r="F5" t="n">
-        <v>19.94390974231333</v>
+        <v>3.240885333125916</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>25.65101983263667</v>
+        <v>4.168290722803459</v>
       </c>
       <c r="D6" t="n">
-        <v>26.61275758644421</v>
+        <v>4.324573107797185</v>
       </c>
       <c r="E6" t="n">
-        <v>19.59054581147163</v>
+        <v>3.183463694364141</v>
       </c>
       <c r="F6" t="n">
-        <v>19.94390974231333</v>
+        <v>3.240885333125916</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>19.68301965874677</v>
+        <v>3.198490694546349</v>
       </c>
       <c r="D7" t="n">
-        <v>18.57500925463157</v>
+        <v>3.018439003877631</v>
       </c>
       <c r="E7" t="n">
-        <v>19.59054581147163</v>
+        <v>3.183463694364141</v>
       </c>
       <c r="F7" t="n">
-        <v>19.94390974231333</v>
+        <v>3.240885333125916</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>42.09719565553416</v>
+        <v>6.840794294024301</v>
       </c>
       <c r="D8" t="n">
-        <v>41.11617896795325</v>
+        <v>6.681379082292403</v>
       </c>
       <c r="E8" t="n">
-        <v>19.59054581147163</v>
+        <v>3.183463694364141</v>
       </c>
       <c r="F8" t="n">
-        <v>19.94390974231333</v>
+        <v>3.240885333125916</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>62.96842507004342</v>
+        <v>10.23236907388206</v>
       </c>
       <c r="D9" t="n">
-        <v>64.73053434709787</v>
+        <v>10.5187118314034</v>
       </c>
       <c r="E9" t="n">
-        <v>19.59054581147163</v>
+        <v>3.183463694364141</v>
       </c>
       <c r="F9" t="n">
-        <v>19.94390974231333</v>
+        <v>3.240885333125916</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>24.42212562123779</v>
+        <v>3.968595413451141</v>
       </c>
       <c r="D10" t="n">
-        <v>25.31295901965427</v>
+        <v>4.113355840693818</v>
       </c>
       <c r="E10" t="n">
-        <v>19.59054581147163</v>
+        <v>3.183463694364141</v>
       </c>
       <c r="F10" t="n">
-        <v>19.94390974231333</v>
+        <v>3.240885333125916</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>65.58069222961105</v>
+        <v>10.65686248731179</v>
       </c>
       <c r="D11" t="n">
-        <v>65.22872771057456</v>
+        <v>10.59966825296837</v>
       </c>
       <c r="E11" t="n">
-        <v>19.59054581147163</v>
+        <v>3.183463694364141</v>
       </c>
       <c r="F11" t="n">
-        <v>19.94390974231333</v>
+        <v>3.240885333125916</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>35.63147594442678</v>
+        <v>5.790114840969352</v>
       </c>
       <c r="D12" t="n">
-        <v>36.29340201042822</v>
+        <v>5.897677826694586</v>
       </c>
       <c r="E12" t="n">
-        <v>19.59054581147163</v>
+        <v>3.183463694364141</v>
       </c>
       <c r="F12" t="n">
-        <v>19.94390974231333</v>
+        <v>3.240885333125916</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>26.74529909923589</v>
+        <v>4.346111103625832</v>
       </c>
       <c r="D13" t="n">
-        <v>28.74570315647544</v>
+        <v>4.67117676292726</v>
       </c>
       <c r="E13" t="n">
-        <v>19.59054581147163</v>
+        <v>3.183463694364141</v>
       </c>
       <c r="F13" t="n">
-        <v>19.94390974231333</v>
+        <v>3.240885333125916</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>45.10413841214844</v>
+        <v>7.329422491974122</v>
       </c>
       <c r="D14" t="n">
-        <v>46.58466139594869</v>
+        <v>7.570007476841662</v>
       </c>
       <c r="E14" t="n">
-        <v>19.59054581147163</v>
+        <v>3.183463694364141</v>
       </c>
       <c r="F14" t="n">
-        <v>19.94390974231333</v>
+        <v>3.240885333125916</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -896,16 +896,16 @@
         <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>85.0999491742477</v>
+        <v>13.82874174081525</v>
       </c>
       <c r="D15" t="n">
-        <v>87.56156519743308</v>
+        <v>14.22875434458288</v>
       </c>
       <c r="E15" t="n">
-        <v>19.59054581147163</v>
+        <v>3.183463694364141</v>
       </c>
       <c r="F15" t="n">
-        <v>19.94390974231333</v>
+        <v>3.240885333125916</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -928,16 +928,16 @@
         <v>15</v>
       </c>
       <c r="C16" t="n">
-        <v>62.92478584944212</v>
+        <v>10.22527770053434</v>
       </c>
       <c r="D16" t="n">
-        <v>65.33302756400904</v>
+        <v>10.61661697915147</v>
       </c>
       <c r="E16" t="n">
-        <v>19.59054581147163</v>
+        <v>3.183463694364141</v>
       </c>
       <c r="F16" t="n">
-        <v>19.94390974231333</v>
+        <v>3.240885333125916</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
